--- a/DATA/bd_tesis.xlsx
+++ b/DATA/bd_tesis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebasteitor\Desktop\MODELOS ECONOMETRICOS\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8381C0-F436-40A6-A479-FB2824A37399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698DDAC1-CB59-4692-8DCE-AC2885A0299C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11610" yWindow="0" windowWidth="26895" windowHeight="15585" xr2:uid="{3A7A9CE9-36D3-406C-942F-B2B38294790B}"/>
+    <workbookView xWindow="10140" yWindow="0" windowWidth="17280" windowHeight="15585" xr2:uid="{3A7A9CE9-36D3-406C-942F-B2B38294790B}"/>
   </bookViews>
   <sheets>
     <sheet name="bdat_tes" sheetId="9" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="205">
   <si>
     <t>Fecha</t>
   </si>
@@ -547,6 +547,117 @@
   </si>
   <si>
     <t>Índice de precios Lima Metropolitana (índice Dic.2021 = 100) - Índice de Precios al Consumidor (IPC)</t>
+  </si>
+  <si>
+    <t>2016Q1</t>
+  </si>
+  <si>
+    <t>2016Q2</t>
+  </si>
+  <si>
+    <t>2016Q3</t>
+  </si>
+  <si>
+    <t>2016Q4</t>
+  </si>
+  <si>
+    <t>2017Q1</t>
+  </si>
+  <si>
+    <t>2017Q2</t>
+  </si>
+  <si>
+    <t>2017Q3</t>
+  </si>
+  <si>
+    <t>2017Q4</t>
+  </si>
+  <si>
+    <t>2018Q1</t>
+  </si>
+  <si>
+    <t>2018Q2</t>
+  </si>
+  <si>
+    <t>2018Q3</t>
+  </si>
+  <si>
+    <t>2018Q4</t>
+  </si>
+  <si>
+    <t>2019Q1</t>
+  </si>
+  <si>
+    <t>2019Q2</t>
+  </si>
+  <si>
+    <t>2019Q3</t>
+  </si>
+  <si>
+    <t>2019Q4</t>
+  </si>
+  <si>
+    <t>2020Q1</t>
+  </si>
+  <si>
+    <t>2020Q2</t>
+  </si>
+  <si>
+    <t>2020Q3</t>
+  </si>
+  <si>
+    <t>2020Q4</t>
+  </si>
+  <si>
+    <t>2021Q1</t>
+  </si>
+  <si>
+    <t>2021Q2</t>
+  </si>
+  <si>
+    <t>2021Q3</t>
+  </si>
+  <si>
+    <t>2021Q4</t>
+  </si>
+  <si>
+    <t>2022Q1</t>
+  </si>
+  <si>
+    <t>2022Q2</t>
+  </si>
+  <si>
+    <t>2022Q3</t>
+  </si>
+  <si>
+    <t>2022Q4</t>
+  </si>
+  <si>
+    <t>2023Q1</t>
+  </si>
+  <si>
+    <t>2023Q2</t>
+  </si>
+  <si>
+    <t>2023Q3</t>
+  </si>
+  <si>
+    <t>2023Q4</t>
+  </si>
+  <si>
+    <t>2024Q1</t>
+  </si>
+  <si>
+    <t>2024Q2</t>
+  </si>
+  <si>
+    <t>2024Q3</t>
+  </si>
+  <si>
+    <t>2024Q4</t>
+  </si>
+  <si>
+    <t>Año</t>
   </si>
 </sst>
 </file>
@@ -6356,7 +6467,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
@@ -6378,8 +6489,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>11</v>
+      <c r="A2" t="s">
+        <v>168</v>
       </c>
       <c r="B2" s="5">
         <v>12057.93</v>
@@ -6402,7 +6513,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="B3" s="5">
         <v>13856.9</v>
@@ -6425,7 +6536,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="B4" s="5">
         <v>15296.98</v>
@@ -6448,7 +6559,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>171</v>
       </c>
       <c r="B5" s="5">
         <v>15566.96</v>
@@ -6471,7 +6582,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="B6" s="5">
         <v>15757.01</v>
@@ -6494,7 +6605,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>173</v>
       </c>
       <c r="B7" s="5">
         <v>16132.87</v>
@@ -6517,7 +6628,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>174</v>
       </c>
       <c r="B8" s="5">
         <v>18538.27</v>
@@ -6540,7 +6651,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="B9" s="5">
         <v>19974.38</v>
@@ -6563,7 +6674,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="B10" s="5">
         <v>20558.84</v>
@@ -6586,7 +6697,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="B11" s="5">
         <v>19800.259999999998</v>
@@ -6609,7 +6720,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="B12" s="5">
         <v>19564.07</v>
@@ -6632,7 +6743,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>179</v>
       </c>
       <c r="B13" s="5">
         <v>19350.400000000001</v>
@@ -6655,7 +6766,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>180</v>
       </c>
       <c r="B14" s="5">
         <v>21098.07</v>
@@ -6678,7 +6789,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
       <c r="B15" s="5">
         <v>20622.79</v>
@@ -6701,7 +6812,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="B16" s="5">
         <v>19602.71</v>
@@ -6724,7 +6835,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>183</v>
       </c>
       <c r="B17" s="5">
         <v>20526.13</v>
@@ -6747,7 +6858,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="B18" s="5">
         <v>14463.96</v>
@@ -6770,7 +6881,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="B19" s="5">
         <v>16878</v>
@@ -6793,7 +6904,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>186</v>
       </c>
       <c r="B20" s="5">
         <v>17948.78</v>
@@ -6816,7 +6927,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>187</v>
       </c>
       <c r="B21" s="5">
         <v>20822.150000000001</v>
@@ -6839,7 +6950,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="B22" s="5">
         <v>21372.03</v>
@@ -6862,7 +6973,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="B23" s="5">
         <v>18850.91</v>
@@ -6885,7 +6996,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>190</v>
       </c>
       <c r="B24" s="5">
         <v>18279.150000000001</v>
@@ -6908,7 +7019,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>191</v>
       </c>
       <c r="B25" s="5">
         <v>21082.9</v>
@@ -6931,7 +7042,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="B26" s="5">
         <v>24915.5</v>
@@ -6954,7 +7065,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>193</v>
       </c>
       <c r="B27" s="5">
         <v>18388.82</v>
@@ -6977,7 +7088,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>194</v>
       </c>
       <c r="B28" s="5">
         <v>19448.060000000001</v>
@@ -7000,7 +7111,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="B29" s="5">
         <v>21330.51</v>
@@ -7023,7 +7134,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>196</v>
       </c>
       <c r="B30" s="5">
         <v>21898.03</v>
@@ -7046,7 +7157,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>197</v>
       </c>
       <c r="B31" s="5">
         <v>22329.75</v>
@@ -7069,7 +7180,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>198</v>
       </c>
       <c r="B32" s="5">
         <v>22528.400000000001</v>
@@ -7092,7 +7203,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>199</v>
       </c>
       <c r="B33" s="5">
         <v>25960.01</v>
@@ -7115,7 +7226,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="B34" s="5">
         <v>28366.99</v>
@@ -7138,7 +7249,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="B35" s="5">
         <v>29895.87</v>
@@ -7161,7 +7272,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>202</v>
       </c>
       <c r="B36" s="5">
         <v>29942.23</v>
@@ -7184,7 +7295,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>203</v>
       </c>
       <c r="B37" s="5">
         <v>28960.95</v>

--- a/DATA/bd_tesis.xlsx
+++ b/DATA/bd_tesis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebasteitor\Desktop\MODELOS ECONOMETRICOS\DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gmendoza\Desktop\Repositorios\MODELOS-ECONOMETRICOS\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698DDAC1-CB59-4692-8DCE-AC2885A0299C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA5DFA1-2885-4D52-99A5-7F8F41EC100D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="17280" windowHeight="15585" xr2:uid="{3A7A9CE9-36D3-406C-942F-B2B38294790B}"/>
+    <workbookView xWindow="9660" yWindow="0" windowWidth="16005" windowHeight="15585" xr2:uid="{3A7A9CE9-36D3-406C-942F-B2B38294790B}"/>
   </bookViews>
   <sheets>
     <sheet name="bdat_tes" sheetId="9" r:id="rId1"/>
@@ -767,7 +767,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1254,7 +1254,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1741,7 +1741,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2228,7 +2228,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2715,7 +2715,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">

--- a/DATA/bd_tesis.xlsx
+++ b/DATA/bd_tesis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gmendoza\Desktop\Repositorios\MODELOS-ECONOMETRICOS\DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebasteitor\Desktop\MODELOS ECONOMETRICOS\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA5DFA1-2885-4D52-99A5-7F8F41EC100D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B894BD2F-1527-4049-AF59-A5195D814991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9660" yWindow="0" windowWidth="16005" windowHeight="15585" xr2:uid="{3A7A9CE9-36D3-406C-942F-B2B38294790B}"/>
+    <workbookView xWindow="7155" yWindow="0" windowWidth="28695" windowHeight="15585" xr2:uid="{3A7A9CE9-36D3-406C-942F-B2B38294790B}"/>
   </bookViews>
   <sheets>
     <sheet name="bdat_tes" sheetId="9" r:id="rId1"/>
@@ -767,7 +767,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1254,7 +1254,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1741,7 +1741,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2228,7 +2228,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2715,7 +2715,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">

--- a/DATA/bd_tesis.xlsx
+++ b/DATA/bd_tesis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29421"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebasteitor\Desktop\MODELOS ECONOMETRICOS\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B894BD2F-1527-4049-AF59-A5195D814991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3549E5-884A-43E3-B26D-DECB7F0D4D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7155" yWindow="0" windowWidth="28695" windowHeight="15585" xr2:uid="{3A7A9CE9-36D3-406C-942F-B2B38294790B}"/>
+    <workbookView xWindow="5856" yWindow="0" windowWidth="17280" windowHeight="12336" xr2:uid="{3A7A9CE9-36D3-406C-942F-B2B38294790B}"/>
   </bookViews>
   <sheets>
     <sheet name="bdat_tes" sheetId="9" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="INFLACIÓN" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/DATA/bd_tesis.xlsx
+++ b/DATA/bd_tesis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29421"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29509"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebasteitor\Desktop\MODELOS ECONOMETRICOS\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3549E5-884A-43E3-B26D-DECB7F0D4D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A353A28E-6324-427A-91B1-73C2FF35FFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5856" yWindow="0" windowWidth="17280" windowHeight="12336" xr2:uid="{3A7A9CE9-36D3-406C-942F-B2B38294790B}"/>
+    <workbookView xWindow="1680" yWindow="0" windowWidth="18660" windowHeight="15585" xr2:uid="{3A7A9CE9-36D3-406C-942F-B2B38294790B}"/>
   </bookViews>
   <sheets>
     <sheet name="bdat_tes" sheetId="9" r:id="rId1"/>
@@ -23,7 +23,6 @@
     <sheet name="INFLACIÓN" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="204">
   <si>
     <t>Fecha</t>
   </si>
@@ -548,9 +547,6 @@
   </si>
   <si>
     <t>Índice de precios Lima Metropolitana (índice Dic.2021 = 100) - Índice de Precios al Consumidor (IPC)</t>
-  </si>
-  <si>
-    <t>2016Q1</t>
   </si>
   <si>
     <t>2016Q2</t>
@@ -6463,12 +6459,12 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
@@ -6485,837 +6481,881 @@
       <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="5">
-        <v>12057.93</v>
-      </c>
-      <c r="C2" s="10">
-        <v>118217.24559821399</v>
-      </c>
-      <c r="D2" s="5">
-        <v>101.638824623758</v>
-      </c>
-      <c r="E2" s="5">
-        <v>4.166666666666667</v>
-      </c>
-      <c r="F2" s="5">
-        <v>85.138244173322434</v>
-      </c>
-      <c r="G2" s="10">
-        <v>4754.9236666666666</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="9">
+        <v>0.14919393295532468</v>
+      </c>
+      <c r="C2" s="9">
+        <v>5.912813064271405E-2</v>
+      </c>
+      <c r="D2" s="9">
+        <v>-2.1335855653557112E-2</v>
+      </c>
+      <c r="E2" s="9">
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="F2" s="9">
+        <v>6.5466894888199789E-3</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="5">
-        <v>13856.9</v>
-      </c>
-      <c r="C3" s="10">
-        <v>125207.210340167</v>
-      </c>
-      <c r="D3" s="5">
-        <v>99.470273332788295</v>
-      </c>
-      <c r="E3" s="5">
-        <v>4.25</v>
-      </c>
-      <c r="F3" s="5">
-        <v>85.69561782154851</v>
-      </c>
-      <c r="G3" s="10">
-        <v>4807.559666666667</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="9">
+        <v>0.1039251203371605</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1.1654966868268835E-2</v>
+      </c>
+      <c r="D3" s="9">
+        <v>1.2581384408587581E-3</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9">
+        <v>5.5331049686506706E-3</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="5">
-        <v>15296.98</v>
-      </c>
-      <c r="C4" s="10">
-        <v>126666.49622835001</v>
-      </c>
-      <c r="D4" s="5">
-        <v>99.595420707391</v>
-      </c>
-      <c r="E4" s="5">
-        <v>4.25</v>
-      </c>
-      <c r="F4" s="5">
-        <v>86.169780670308512</v>
-      </c>
-      <c r="G4" s="10">
-        <v>4835.0423333333338</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="9">
+        <v>1.7649235339262992E-2</v>
+      </c>
+      <c r="C4" s="9">
+        <v>3.8006986072852911E-2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>-9.9985898154543174E-3</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
+        <v>9.7833510130842516E-3</v>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="5">
-        <v>15566.96</v>
-      </c>
-      <c r="C5" s="10">
-        <v>131480.70798639799</v>
-      </c>
-      <c r="D5" s="5">
-        <v>98.599606948240194</v>
-      </c>
-      <c r="E5" s="5">
-        <v>4.25</v>
-      </c>
-      <c r="F5" s="5">
-        <v>87.012809881326618</v>
-      </c>
-      <c r="G5" s="10">
-        <v>4931.0093333333334</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="9">
+        <v>1.2208549389219225E-2</v>
+      </c>
+      <c r="C5" s="9">
+        <v>-8.0341440774130857E-2</v>
+      </c>
+      <c r="D5" s="9">
+        <v>-3.8330897199060354E-2</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9">
+        <v>1.2131000957281257E-2</v>
+      </c>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>172</v>
       </c>
-      <c r="B6" s="5">
-        <v>15757.01</v>
-      </c>
-      <c r="C6" s="10">
-        <v>120917.358472768</v>
-      </c>
-      <c r="D6" s="5">
-        <v>94.820195550439436</v>
-      </c>
-      <c r="E6" s="5">
-        <v>4.25</v>
-      </c>
-      <c r="F6" s="5">
-        <v>88.068362361292728</v>
-      </c>
-      <c r="G6" s="10">
-        <v>4865.3516666666665</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="9">
+        <v>2.3853510278917245E-2</v>
+      </c>
+      <c r="C6" s="9">
+        <v>6.2898770182428843E-2</v>
+      </c>
+      <c r="D6" s="9">
+        <v>5.1702456617896964E-4</v>
+      </c>
+      <c r="E6" s="9">
+        <v>-3.9215686274509887E-2</v>
+      </c>
+      <c r="F6" s="9">
+        <v>3.7586927491435329E-3</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="5">
-        <v>16132.87</v>
-      </c>
-      <c r="C7" s="10">
-        <v>128522.91161441299</v>
-      </c>
-      <c r="D7" s="5">
-        <v>94.869219920908904</v>
-      </c>
-      <c r="E7" s="5">
-        <v>4.083333333333333</v>
-      </c>
-      <c r="F7" s="5">
-        <v>88.399384276329059</v>
-      </c>
-      <c r="G7" s="10">
-        <v>4888.4089999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="9">
+        <v>0.14909932330701237</v>
+      </c>
+      <c r="C7" s="9">
+        <v>1.3294439771113886E-2</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1.8671513635743819E-2</v>
+      </c>
+      <c r="E7" s="9">
+        <v>-0.10204081632653061</v>
+      </c>
+      <c r="F7" s="9">
+        <v>3.9280697457773073E-3</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>174</v>
       </c>
-      <c r="B8" s="5">
-        <v>18538.27</v>
-      </c>
-      <c r="C8" s="10">
-        <v>130231.55172207901</v>
-      </c>
-      <c r="D8" s="5">
-        <v>96.640571854274526</v>
-      </c>
-      <c r="E8" s="5">
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="F8" s="5">
-        <v>88.746623223250253</v>
-      </c>
-      <c r="G8" s="10">
-        <v>4930.2760000000007</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="9">
+        <v>7.7467314911261909E-2</v>
+      </c>
+      <c r="C8" s="9">
+        <v>3.3031360802312282E-2</v>
+      </c>
+      <c r="D8" s="9">
+        <v>9.1259676959432046E-3</v>
+      </c>
+      <c r="E8" s="9">
+        <v>-9.0909090909090828E-2</v>
+      </c>
+      <c r="F8" s="9">
+        <v>-3.3679902675013418E-3</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>175</v>
       </c>
-      <c r="B9" s="5">
-        <v>19974.38</v>
-      </c>
-      <c r="C9" s="10">
-        <v>134533.27709485599</v>
-      </c>
-      <c r="D9" s="5">
-        <v>97.522510591134122</v>
-      </c>
-      <c r="E9" s="5">
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="F9" s="5">
-        <v>88.447725459960736</v>
-      </c>
-      <c r="G9" s="10">
-        <v>5057.2423333333327</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="9">
+        <v>2.926048267831094E-2</v>
+      </c>
+      <c r="C9" s="9">
+        <v>-7.2741632978404414E-2</v>
+      </c>
+      <c r="D9" s="9">
+        <v>2.8319708578898428E-2</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-0.12500000000000011</v>
+      </c>
+      <c r="F9" s="9">
+        <v>4.9625514034821183E-3</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>176</v>
       </c>
-      <c r="B10" s="5">
-        <v>20558.84</v>
-      </c>
-      <c r="C10" s="10">
-        <v>124747.10682904</v>
-      </c>
-      <c r="D10" s="5">
-        <v>100.28431967095757</v>
-      </c>
-      <c r="E10" s="5">
-        <v>2.9166666666666665</v>
-      </c>
-      <c r="F10" s="5">
-        <v>88.886651844076866</v>
-      </c>
-      <c r="G10" s="10">
-        <v>5019.2286666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="9">
+        <v>-3.6897996190446647E-2</v>
+      </c>
+      <c r="C10" s="9">
+        <v>8.7932086770740714E-2</v>
+      </c>
+      <c r="D10" s="9">
+        <v>-1.104286764859097E-2</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-5.7142857142857051E-2</v>
+      </c>
+      <c r="F10" s="9">
+        <v>3.9400432213168024E-3</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>177</v>
       </c>
-      <c r="B11" s="5">
-        <v>19800.259999999998</v>
-      </c>
-      <c r="C11" s="10">
-        <v>135716.38025113</v>
-      </c>
-      <c r="D11" s="5">
-        <v>99.176893201602198</v>
-      </c>
-      <c r="E11" s="5">
-        <v>2.75</v>
-      </c>
-      <c r="F11" s="5">
-        <v>89.236869094140673</v>
-      </c>
-      <c r="G11" s="10">
-        <v>5081.5293333333329</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="9">
+        <v>-1.192863124019572E-2</v>
+      </c>
+      <c r="C11" s="9">
+        <v>-1.7010144267289196E-2</v>
+      </c>
+      <c r="D11" s="9">
+        <v>-2.8631500721197134E-2</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9">
+        <v>7.650291311653179E-3</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>178</v>
       </c>
-      <c r="B12" s="5">
-        <v>19564.07</v>
-      </c>
-      <c r="C12" s="10">
-        <v>133407.82504362401</v>
-      </c>
-      <c r="D12" s="5">
-        <v>96.337309912374437</v>
-      </c>
-      <c r="E12" s="5">
-        <v>2.75</v>
-      </c>
-      <c r="F12" s="5">
-        <v>89.919557138450713</v>
-      </c>
-      <c r="G12" s="10">
-        <v>5135.78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="9">
+        <v>-1.0921551599437085E-2</v>
+      </c>
+      <c r="C12" s="9">
+        <v>5.4994362507386096E-2</v>
+      </c>
+      <c r="D12" s="9">
+        <v>6.9169469590943944E-3</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>3.9609427561897448E-3</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>179</v>
       </c>
-      <c r="B13" s="5">
-        <v>19350.400000000001</v>
-      </c>
-      <c r="C13" s="10">
-        <v>140744.50333539501</v>
-      </c>
-      <c r="D13" s="5">
-        <v>97.003669975220177</v>
-      </c>
-      <c r="E13" s="5">
-        <v>2.75</v>
-      </c>
-      <c r="F13" s="5">
-        <v>90.275723356938059</v>
-      </c>
-      <c r="G13" s="10">
-        <v>5252.7996666666668</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="9">
+        <v>9.0316996031089669E-2</v>
+      </c>
+      <c r="C13" s="9">
+        <v>-9.2406698353315164E-2</v>
+      </c>
+      <c r="D13" s="9">
+        <v>1.9674834622016579E-3</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9">
+        <v>5.5543024761930404E-3</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>180</v>
       </c>
-      <c r="B14" s="5">
-        <v>21098.07</v>
-      </c>
-      <c r="C14" s="10">
-        <v>127738.76847079401</v>
-      </c>
-      <c r="D14" s="5">
-        <v>97.194523091669296</v>
-      </c>
-      <c r="E14" s="5">
-        <v>2.75</v>
-      </c>
-      <c r="F14" s="5">
-        <v>90.777142030719617</v>
-      </c>
-      <c r="G14" s="10">
-        <v>5160.6616666666669</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="9">
+        <v>-2.2527179026327948E-2</v>
+      </c>
+      <c r="C14" s="9">
+        <v>7.4660439259515154E-2</v>
+      </c>
+      <c r="D14" s="9">
+        <v>-1.1202705787264788E-2</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>7.9743021134019987E-3</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>181</v>
       </c>
-      <c r="B15" s="5">
-        <v>20622.79</v>
-      </c>
-      <c r="C15" s="10">
-        <v>137275.801035293</v>
-      </c>
-      <c r="D15" s="5">
-        <v>96.105681445339812</v>
-      </c>
-      <c r="E15" s="5">
-        <v>2.75</v>
-      </c>
-      <c r="F15" s="5">
-        <v>91.501026386263774</v>
-      </c>
-      <c r="G15" s="10">
-        <v>5183.2446666666665</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="9">
+        <v>-4.9463724355434002E-2</v>
+      </c>
+      <c r="C15" s="9">
+        <v>4.7634529856421803E-3</v>
+      </c>
+      <c r="D15" s="9">
+        <v>-3.2340244748559899E-3</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-6.0606060606060552E-2</v>
+      </c>
+      <c r="F15" s="9">
+        <v>2.3779448429230854E-3</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>182</v>
       </c>
-      <c r="B16" s="5">
-        <v>19602.71</v>
-      </c>
-      <c r="C16" s="10">
-        <v>137929.707859591</v>
-      </c>
-      <c r="D16" s="5">
-        <v>95.794873319372869</v>
-      </c>
-      <c r="E16" s="5">
-        <v>2.5833333333333335</v>
-      </c>
-      <c r="F16" s="5">
-        <v>91.718610780081164</v>
-      </c>
-      <c r="G16" s="10">
-        <v>5272.8429999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="9">
+        <v>4.7106752076626179E-2</v>
+      </c>
+      <c r="C16" s="9">
+        <v>4.1466548767269629E-2</v>
+      </c>
+      <c r="D16" s="9">
+        <v>7.8911421764371603E-3</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-9.6774193548387122E-2</v>
+      </c>
+      <c r="F16" s="9">
+        <v>2.7971269480104866E-3</v>
+      </c>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>183</v>
       </c>
-      <c r="B17" s="5">
-        <v>20526.13</v>
-      </c>
-      <c r="C17" s="10">
-        <v>143649.17681700599</v>
-      </c>
-      <c r="D17" s="5">
-        <v>96.550804284509823</v>
-      </c>
-      <c r="E17" s="5">
-        <v>2.3333333333333335</v>
-      </c>
-      <c r="F17" s="5">
-        <v>91.975159377928208</v>
-      </c>
-      <c r="G17" s="10">
-        <v>5438.4636666666665</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="9">
+        <v>-0.29533916037752861</v>
+      </c>
+      <c r="C17" s="9">
+        <v>-0.14246994408707359</v>
+      </c>
+      <c r="D17" s="9">
+        <v>9.33980260831202E-3</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-0.1785714285714286</v>
+      </c>
+      <c r="F17" s="9">
+        <v>5.4426384139978357E-3</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>184</v>
       </c>
-      <c r="B18" s="5">
-        <v>14463.96</v>
-      </c>
-      <c r="C18" s="10">
-        <v>123183.486627733</v>
-      </c>
-      <c r="D18" s="5">
-        <v>97.452569738200921</v>
-      </c>
-      <c r="E18" s="5">
-        <v>1.9166666666666667</v>
-      </c>
-      <c r="F18" s="5">
-        <v>92.475746913492102</v>
-      </c>
-      <c r="G18" s="10">
-        <v>5298.0010000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="9">
+        <v>0.16690035094123612</v>
+      </c>
+      <c r="C18" s="9">
+        <v>-0.22044342584274235</v>
+      </c>
+      <c r="D18" s="9">
+        <v>-3.0953394232967835E-2</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-0.86956521739130432</v>
+      </c>
+      <c r="F18" s="9">
+        <v>6.2976738199760351E-3</v>
+      </c>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="5">
-        <v>16878</v>
-      </c>
-      <c r="C19" s="10">
-        <v>96028.496828261894</v>
-      </c>
-      <c r="D19" s="5">
-        <v>94.436081928078593</v>
-      </c>
-      <c r="E19" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="F19" s="5">
-        <v>93.058129003811928</v>
-      </c>
-      <c r="G19" s="10">
-        <v>4807.8466666666673</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="9">
+        <v>6.3442350989453722E-2</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0.31155199098279596</v>
+      </c>
+      <c r="D19" s="9">
+        <v>6.1841387345781929E-2</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9">
+        <v>3.2433347841347437E-3</v>
+      </c>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>186</v>
       </c>
-      <c r="B20" s="5">
-        <v>17948.78</v>
-      </c>
-      <c r="C20" s="10">
-        <v>125946.366206192</v>
-      </c>
-      <c r="D20" s="5">
-        <v>100.2761402500109</v>
-      </c>
-      <c r="E20" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="F20" s="5">
-        <v>93.35994767055648</v>
-      </c>
-      <c r="G20" s="10">
-        <v>4971.4430000000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="9">
+        <v>0.16008720369852458</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0.12469146930068309</v>
+      </c>
+      <c r="D20" s="9">
+        <v>4.1294202009814374E-2</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>4.3442853994482E-3</v>
+      </c>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>187</v>
       </c>
-      <c r="B21" s="5">
-        <v>20822.150000000001</v>
-      </c>
-      <c r="C21" s="10">
-        <v>141650.803661524</v>
-      </c>
-      <c r="D21" s="5">
-        <v>104.41696344225933</v>
-      </c>
-      <c r="E21" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="F21" s="5">
-        <v>93.76552992811493</v>
-      </c>
-      <c r="G21" s="10">
-        <v>5247.2323333333334</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="9">
+        <v>2.6408416037728921E-2</v>
+      </c>
+      <c r="C21" s="9">
+        <v>-9.3837556732595528E-2</v>
+      </c>
+      <c r="D21" s="9">
+        <v>2.8133233843909311E-2</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>1.1476555106540332E-2</v>
+      </c>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>188</v>
       </c>
-      <c r="B22" s="5">
-        <v>21372.03</v>
-      </c>
-      <c r="C22" s="10">
-        <v>128358.638336718</v>
-      </c>
-      <c r="D22" s="5">
-        <v>107.35455029205134</v>
-      </c>
-      <c r="E22" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="F22" s="5">
-        <v>94.841635199428893</v>
-      </c>
-      <c r="G22" s="10">
-        <v>5108.6343333333334</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="9">
+        <v>-0.11796352522432352</v>
+      </c>
+      <c r="C22" s="9">
+        <v>6.2592245758630316E-2</v>
+      </c>
+      <c r="D22" s="9">
+        <v>3.8443097404702309E-2</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>7.6378056143793227E-3</v>
+      </c>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>189</v>
       </c>
-      <c r="B23" s="5">
-        <v>18850.91</v>
-      </c>
-      <c r="C23" s="10">
-        <v>136392.89377273299</v>
-      </c>
-      <c r="D23" s="5">
-        <v>111.48159172576668</v>
-      </c>
-      <c r="E23" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="F23" s="5">
-        <v>95.566017173232012</v>
-      </c>
-      <c r="G23" s="10">
-        <v>5139.9750000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="9">
+        <v>-3.033063125334523E-2</v>
+      </c>
+      <c r="C23" s="9">
+        <v>3.1264237507075299E-2</v>
+      </c>
+      <c r="D23" s="9">
+        <v>4.2108669222699513E-2</v>
+      </c>
+      <c r="E23" s="9">
+        <v>1.3333333333333335</v>
+      </c>
+      <c r="F23" s="9">
+        <v>2.2494761022685106E-2</v>
+      </c>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>190</v>
       </c>
-      <c r="B24" s="5">
-        <v>18279.150000000001</v>
-      </c>
-      <c r="C24" s="10">
-        <v>140657.11359792101</v>
-      </c>
-      <c r="D24" s="5">
-        <v>116.17593319616701</v>
-      </c>
-      <c r="E24" s="5">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F24" s="5">
-        <v>97.715751891433698</v>
-      </c>
-      <c r="G24" s="10">
-        <v>5321.1633333333339</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="9">
+        <v>0.15338514099397393</v>
+      </c>
+      <c r="C24" s="9">
+        <v>4.1337365463213427E-2</v>
+      </c>
+      <c r="D24" s="9">
+        <v>-1.5486835904248708E-2</v>
+      </c>
+      <c r="E24" s="9">
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="F24" s="9">
+        <v>1.6869004172735069E-2</v>
+      </c>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>191</v>
       </c>
-      <c r="B25" s="5">
-        <v>21082.9</v>
-      </c>
-      <c r="C25" s="10">
-        <v>146471.50810771901</v>
-      </c>
-      <c r="D25" s="5">
-        <v>114.37673558273501</v>
-      </c>
-      <c r="E25" s="5">
-        <v>2</v>
-      </c>
-      <c r="F25" s="5">
-        <v>99.364119317832248</v>
-      </c>
-      <c r="G25" s="10">
-        <v>5564.9929999999995</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="9">
+        <v>0.18178713554586889</v>
+      </c>
+      <c r="C25" s="9">
+        <v>-8.961278199274092E-2</v>
+      </c>
+      <c r="D25" s="9">
+        <v>-5.0796579337109571E-2</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="F25" s="9">
+        <v>1.3856182274714968E-2</v>
+      </c>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>192</v>
       </c>
-      <c r="B26" s="5">
-        <v>24915.5</v>
-      </c>
-      <c r="C26" s="10">
-        <v>133345.788783514</v>
-      </c>
-      <c r="D26" s="5">
-        <v>108.566788659387</v>
-      </c>
-      <c r="E26" s="5">
-        <v>3.5</v>
-      </c>
-      <c r="F26" s="5">
-        <v>100.74092666666665</v>
-      </c>
-      <c r="G26" s="10">
-        <v>5497.7006666666675</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="9">
+        <v>-0.26195259978728103</v>
+      </c>
+      <c r="C26" s="9">
+        <v>5.767662061738732E-2</v>
+      </c>
+      <c r="D26" s="9">
+        <v>-5.0393951510221968E-2</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="F26" s="9">
+        <v>2.7279396344643603E-2</v>
+      </c>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>193</v>
       </c>
-      <c r="B27" s="5">
-        <v>18388.82</v>
-      </c>
-      <c r="C27" s="10">
-        <v>141036.723254107</v>
-      </c>
-      <c r="D27" s="5">
-        <v>103.09567917606533</v>
-      </c>
-      <c r="E27" s="5">
-        <v>5</v>
-      </c>
-      <c r="F27" s="5">
-        <v>103.48907833333334</v>
-      </c>
-      <c r="G27" s="10">
-        <v>5535.6620000000003</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="9">
+        <v>5.7602391018020782E-2</v>
+      </c>
+      <c r="C27" s="9">
+        <v>1.776898136712779E-2</v>
+      </c>
+      <c r="D27" s="9">
+        <v>-1.2084206166041778E-2</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0.28333333333333344</v>
+      </c>
+      <c r="F27" s="9">
+        <v>2.49961771328302E-2</v>
+      </c>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>194</v>
       </c>
-      <c r="B28" s="5">
-        <v>19448.060000000001</v>
-      </c>
-      <c r="C28" s="10">
-        <v>143542.80216168999</v>
-      </c>
-      <c r="D28" s="5">
-        <v>101.84984973407366</v>
-      </c>
-      <c r="E28" s="5">
-        <v>6.416666666666667</v>
-      </c>
-      <c r="F28" s="5">
-        <v>106.07590966666667</v>
-      </c>
-      <c r="G28" s="10">
-        <v>5635.5710000000008</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="9">
+        <v>9.6793716185573198E-2</v>
+      </c>
+      <c r="C28" s="9">
+        <v>4.1242538244387061E-2</v>
+      </c>
+      <c r="D28" s="9">
+        <v>-2.6884254105918437E-2</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.12987012987012991</v>
+      </c>
+      <c r="F28" s="9">
+        <v>1.5356983551863879E-2</v>
+      </c>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>195</v>
       </c>
-      <c r="B29" s="5">
-        <v>21330.51</v>
-      </c>
-      <c r="C29" s="10">
-        <v>149462.87166954999</v>
-      </c>
-      <c r="D29" s="5">
-        <v>99.111692493173209</v>
-      </c>
-      <c r="E29" s="5">
-        <v>7.25</v>
-      </c>
-      <c r="F29" s="5">
-        <v>107.70491566666668</v>
-      </c>
-      <c r="G29" s="10">
-        <v>5828.7926666666672</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="9">
+        <v>2.6606021140610281E-2</v>
+      </c>
+      <c r="C29" s="9">
+        <v>-0.10881478728471672</v>
+      </c>
+      <c r="D29" s="9">
+        <v>3.8540706574698991E-3</v>
+      </c>
+      <c r="E29" s="9">
+        <v>6.8965517241379226E-2</v>
+      </c>
+      <c r="F29" s="9">
+        <v>1.5494427433236035E-2</v>
+      </c>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>196</v>
       </c>
-      <c r="B30" s="5">
-        <v>21898.03</v>
-      </c>
-      <c r="C30" s="10">
-        <v>133199.101081865</v>
-      </c>
-      <c r="D30" s="5">
-        <v>99.493675959023335</v>
-      </c>
-      <c r="E30" s="5">
-        <v>7.75</v>
-      </c>
-      <c r="F30" s="5">
-        <v>109.37374166666666</v>
-      </c>
-      <c r="G30" s="10">
-        <v>5671.2730000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="9">
+        <v>1.9715015460294971E-2</v>
+      </c>
+      <c r="C30" s="9">
+        <v>5.4265419081406474E-2</v>
+      </c>
+      <c r="D30" s="9">
+        <v>-4.4659792153693867E-2</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9">
+        <v>1.6552166047777206E-2</v>
+      </c>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="5">
-        <v>22329.75</v>
-      </c>
-      <c r="C31" s="10">
-        <v>140427.20612333901</v>
-      </c>
-      <c r="D31" s="5">
-        <v>95.050309070086385</v>
-      </c>
-      <c r="E31" s="5">
-        <v>7.75</v>
-      </c>
-      <c r="F31" s="5">
-        <v>111.18411400000001</v>
-      </c>
-      <c r="G31" s="10">
-        <v>5724.8023333333331</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="9">
+        <v>8.8962034953370406E-3</v>
+      </c>
+      <c r="C31" s="9">
+        <v>1.5454732265219429E-2</v>
+      </c>
+      <c r="D31" s="9">
+        <v>-1.8253340964666798E-2</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-1.0752688172043001E-2</v>
+      </c>
+      <c r="F31" s="9">
+        <v>6.5211354444634217E-3</v>
+      </c>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>198</v>
       </c>
-      <c r="B32" s="5">
-        <v>22528.400000000001</v>
-      </c>
-      <c r="C32" s="10">
-        <v>142597.47099672799</v>
-      </c>
-      <c r="D32" s="5">
-        <v>93.315323369833138</v>
-      </c>
-      <c r="E32" s="5">
-        <v>7.666666666666667</v>
-      </c>
-      <c r="F32" s="5">
-        <v>111.90916066666666</v>
-      </c>
-      <c r="G32" s="10">
-        <v>5740.9830000000002</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="9">
+        <v>0.15232373359847995</v>
+      </c>
+      <c r="C32" s="9">
+        <v>4.4039638019394589E-2</v>
+      </c>
+      <c r="D32" s="9">
+        <v>2.5393759211418176E-2</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-8.6956521739130488E-2</v>
+      </c>
+      <c r="F32" s="9">
+        <v>-1.6059841058825297E-3</v>
+      </c>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>199</v>
       </c>
-      <c r="B33" s="5">
-        <v>25960.01</v>
-      </c>
-      <c r="C33" s="10">
-        <v>148877.412001905</v>
-      </c>
-      <c r="D33" s="5">
-        <v>95.684950222222312</v>
-      </c>
-      <c r="E33" s="5">
-        <v>7</v>
-      </c>
-      <c r="F33" s="5">
-        <v>111.72943633333334</v>
-      </c>
-      <c r="G33" s="10">
-        <v>5866.3753333333334</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="9">
+        <v>9.2718762434991442E-2</v>
+      </c>
+      <c r="C33" s="9">
+        <v>-9.3037395263599665E-2</v>
+      </c>
+      <c r="D33" s="9">
+        <v>-3.935163891088389E-3</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-9.5238095238095233E-2</v>
+      </c>
+      <c r="F33" s="9">
+        <v>9.4659924430715581E-3</v>
+      </c>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>200</v>
       </c>
-      <c r="B34" s="5">
-        <v>28366.99</v>
-      </c>
-      <c r="C34" s="10">
-        <v>135026.24537566199</v>
-      </c>
-      <c r="D34" s="5">
-        <v>95.308414261187238</v>
-      </c>
-      <c r="E34" s="5">
-        <v>6.333333333333333</v>
-      </c>
-      <c r="F34" s="5">
-        <v>112.78706633333333</v>
-      </c>
-      <c r="G34" s="10">
-        <v>5700.8266666666677</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="9">
+        <v>5.3896447948830639E-2</v>
+      </c>
+      <c r="C34" s="9">
+        <v>7.7552922281237446E-2</v>
+      </c>
+      <c r="D34" s="9">
+        <v>-1.7264637671396965E-2</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-7.8947368421052655E-2</v>
+      </c>
+      <c r="F34" s="9">
+        <v>7.842296953203709E-3</v>
+      </c>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>201</v>
       </c>
-      <c r="B35" s="5">
-        <v>29895.87</v>
-      </c>
-      <c r="C35" s="10">
-        <v>145497.92528920801</v>
-      </c>
-      <c r="D35" s="5">
-        <v>93.662949021932434</v>
-      </c>
-      <c r="E35" s="5">
-        <v>5.833333333333333</v>
-      </c>
-      <c r="F35" s="5">
-        <v>113.671576</v>
-      </c>
-      <c r="G35" s="10">
-        <v>5856.5320000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="9">
+        <v>1.5507158681116184E-3</v>
+      </c>
+      <c r="C35" s="9">
+        <v>1.7829107222928853E-2</v>
+      </c>
+      <c r="D35" s="9">
+        <v>1.034392182364563E-2</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-5.7142857142857051E-2</v>
+      </c>
+      <c r="F35" s="9">
+        <v>3.9760247539806226E-3</v>
+      </c>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>202</v>
       </c>
-      <c r="B36" s="5">
-        <v>29942.23</v>
-      </c>
-      <c r="C36" s="10">
-        <v>148092.023399903</v>
-      </c>
-      <c r="D36" s="5">
-        <v>94.631791244387401</v>
-      </c>
-      <c r="E36" s="5">
-        <v>5.5</v>
-      </c>
-      <c r="F36" s="5">
-        <v>114.123537</v>
-      </c>
-      <c r="G36" s="10">
-        <v>5919.8906666666662</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>203</v>
-      </c>
-      <c r="B37" s="5">
-        <v>28960.95</v>
-      </c>
-      <c r="C37" s="10">
-        <v>155150.116522667</v>
-      </c>
-      <c r="D37" s="5">
-        <v>93.427286849745371</v>
-      </c>
-      <c r="E37" s="5">
-        <v>5.083333333333333</v>
-      </c>
-      <c r="F37" s="5">
-        <v>114.05597233333333</v>
-      </c>
-      <c r="G37" s="10">
-        <v>6153.8710000000001</v>
-      </c>
+      <c r="B36" s="9">
+        <v>-3.2772442132733559E-2</v>
+      </c>
+      <c r="C36" s="9">
+        <v>4.7660184260596816E-2</v>
+      </c>
+      <c r="D36" s="9">
+        <v>-1.2728327117167093E-2</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-7.5757575757575801E-2</v>
+      </c>
+      <c r="F36" s="9">
+        <v>-5.9203095560089736E-4</v>
+      </c>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9203,14 +9243,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEEB6EBB-019E-43EB-8617-44B1F19B4F72}">
-  <dimension ref="A2:B112"/>
+  <dimension ref="A2:J112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="2"/>
     <col min="2" max="2" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -9218,295 +9258,835 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>42370</v>
       </c>
       <c r="B3" s="5">
         <v>153.30000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>12057.93</v>
+      </c>
+      <c r="G3">
+        <v>118217.24559821399</v>
+      </c>
+      <c r="H3">
+        <v>101.638824623758</v>
+      </c>
+      <c r="I3">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="J3">
+        <v>85.138244173322434</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>42401</v>
       </c>
       <c r="B4" s="5">
         <v>156</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>13856.9</v>
+      </c>
+      <c r="G4">
+        <v>125207.210340167</v>
+      </c>
+      <c r="H4">
+        <v>99.470273332788295</v>
+      </c>
+      <c r="I4">
+        <v>4.25</v>
+      </c>
+      <c r="J4">
+        <v>85.69561782154851</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>42430</v>
       </c>
       <c r="B5" s="5">
         <v>154.6</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>15296.98</v>
+      </c>
+      <c r="G5">
+        <v>126666.49622835001</v>
+      </c>
+      <c r="H5">
+        <v>99.595420707391</v>
+      </c>
+      <c r="I5">
+        <v>4.25</v>
+      </c>
+      <c r="J5">
+        <v>86.169780670308512</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>42461</v>
       </c>
       <c r="B6" s="5">
         <v>156</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>15566.96</v>
+      </c>
+      <c r="G6">
+        <v>131480.70798639799</v>
+      </c>
+      <c r="H6">
+        <v>98.599606948240194</v>
+      </c>
+      <c r="I6">
+        <v>4.25</v>
+      </c>
+      <c r="J6">
+        <v>87.012809881326618</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>42491</v>
       </c>
       <c r="B7" s="5">
         <v>155.80000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <v>15757.01</v>
+      </c>
+      <c r="G7">
+        <v>120917.358472768</v>
+      </c>
+      <c r="H7">
+        <v>94.820195550439436</v>
+      </c>
+      <c r="I7">
+        <v>4.25</v>
+      </c>
+      <c r="J7">
+        <v>88.068362361292728</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>42522</v>
       </c>
       <c r="B8" s="5">
         <v>155.30000000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <v>16132.87</v>
+      </c>
+      <c r="G8">
+        <v>128522.91161441299</v>
+      </c>
+      <c r="H8">
+        <v>94.869219920908904</v>
+      </c>
+      <c r="I8">
+        <v>4.083333333333333</v>
+      </c>
+      <c r="J8">
+        <v>88.399384276329059</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>42552</v>
       </c>
       <c r="B9" s="5">
         <v>157</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <v>18538.27</v>
+      </c>
+      <c r="G9">
+        <v>130231.55172207901</v>
+      </c>
+      <c r="H9">
+        <v>96.640571854274526</v>
+      </c>
+      <c r="I9">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="J9">
+        <v>88.746623223250253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>42583</v>
       </c>
       <c r="B10" s="5">
         <v>158.30000000000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <v>19974.38</v>
+      </c>
+      <c r="G10">
+        <v>134533.27709485599</v>
+      </c>
+      <c r="H10">
+        <v>97.522510591134122</v>
+      </c>
+      <c r="I10">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="J10">
+        <v>88.447725459960736</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>42614</v>
       </c>
       <c r="B11" s="5">
         <v>158.19999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <v>20558.84</v>
+      </c>
+      <c r="G11">
+        <v>124747.10682904</v>
+      </c>
+      <c r="H11">
+        <v>100.28431967095757</v>
+      </c>
+      <c r="I11">
+        <v>2.9166666666666665</v>
+      </c>
+      <c r="J11">
+        <v>88.886651844076866</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>42644</v>
       </c>
       <c r="B12" s="5">
         <v>157.4</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <v>19800.259999999998</v>
+      </c>
+      <c r="G12">
+        <v>135716.38025113</v>
+      </c>
+      <c r="H12">
+        <v>99.176893201602198</v>
+      </c>
+      <c r="I12">
+        <v>2.75</v>
+      </c>
+      <c r="J12">
+        <v>89.236869094140673</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>42675</v>
       </c>
       <c r="B13" s="5">
         <v>158.1</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <v>19564.07</v>
+      </c>
+      <c r="G13">
+        <v>133407.82504362401</v>
+      </c>
+      <c r="H13">
+        <v>96.337309912374437</v>
+      </c>
+      <c r="I13">
+        <v>2.75</v>
+      </c>
+      <c r="J13">
+        <v>89.919557138450713</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>42705</v>
       </c>
       <c r="B14" s="5">
         <v>159.1</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <v>19350.400000000001</v>
+      </c>
+      <c r="G14">
+        <v>140744.50333539501</v>
+      </c>
+      <c r="H14">
+        <v>97.003669975220177</v>
+      </c>
+      <c r="I14">
+        <v>2.75</v>
+      </c>
+      <c r="J14">
+        <v>90.275723356938059</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>42736</v>
       </c>
       <c r="B15" s="5">
         <v>160</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <v>21098.07</v>
+      </c>
+      <c r="G15">
+        <v>127738.76847079401</v>
+      </c>
+      <c r="H15">
+        <v>97.194523091669296</v>
+      </c>
+      <c r="I15">
+        <v>2.75</v>
+      </c>
+      <c r="J15">
+        <v>90.777142030719617</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>42767</v>
       </c>
       <c r="B16" s="5">
         <v>159.1</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <v>20622.79</v>
+      </c>
+      <c r="G16">
+        <v>137275.801035293</v>
+      </c>
+      <c r="H16">
+        <v>96.105681445339812</v>
+      </c>
+      <c r="I16">
+        <v>2.75</v>
+      </c>
+      <c r="J16">
+        <v>91.501026386263774</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>42795</v>
       </c>
       <c r="B17" s="5">
         <v>157.80000000000001</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <v>19602.71</v>
+      </c>
+      <c r="G17">
+        <v>137929.707859591</v>
+      </c>
+      <c r="H17">
+        <v>95.794873319372869</v>
+      </c>
+      <c r="I17">
+        <v>2.5833333333333335</v>
+      </c>
+      <c r="J17">
+        <v>91.718610780081164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>42826</v>
       </c>
       <c r="B18" s="5">
         <v>158.69999999999999</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <v>20526.13</v>
+      </c>
+      <c r="G18">
+        <v>143649.17681700599</v>
+      </c>
+      <c r="H18">
+        <v>96.550804284509823</v>
+      </c>
+      <c r="I18">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="J18">
+        <v>91.975159377928208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>42856</v>
       </c>
       <c r="B19" s="5">
         <v>159.4</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <v>14463.96</v>
+      </c>
+      <c r="G19">
+        <v>123183.486627733</v>
+      </c>
+      <c r="H19">
+        <v>97.452569738200921</v>
+      </c>
+      <c r="I19">
+        <v>1.9166666666666667</v>
+      </c>
+      <c r="J19">
+        <v>92.475746913492102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>42887</v>
       </c>
       <c r="B20" s="5">
         <v>162.69999999999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <v>16878</v>
+      </c>
+      <c r="G20">
+        <v>96028.496828261894</v>
+      </c>
+      <c r="H20">
+        <v>94.436081928078593</v>
+      </c>
+      <c r="I20">
+        <v>0.25</v>
+      </c>
+      <c r="J20">
+        <v>93.058129003811928</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>42917</v>
       </c>
       <c r="B21" s="5">
         <v>161.80000000000001</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <v>17948.78</v>
+      </c>
+      <c r="G21">
+        <v>125946.366206192</v>
+      </c>
+      <c r="H21">
+        <v>100.2761402500109</v>
+      </c>
+      <c r="I21">
+        <v>0.25</v>
+      </c>
+      <c r="J21">
+        <v>93.35994767055648</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>42948</v>
       </c>
       <c r="B22" s="5">
         <v>162.6</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <v>20822.150000000001</v>
+      </c>
+      <c r="G22">
+        <v>141650.803661524</v>
+      </c>
+      <c r="H22">
+        <v>104.41696344225933</v>
+      </c>
+      <c r="I22">
+        <v>0.25</v>
+      </c>
+      <c r="J22">
+        <v>93.76552992811493</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>42979</v>
       </c>
       <c r="B23" s="5">
         <v>163.9</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <v>21372.03</v>
+      </c>
+      <c r="G23">
+        <v>128358.638336718</v>
+      </c>
+      <c r="H23">
+        <v>107.35455029205134</v>
+      </c>
+      <c r="I23">
+        <v>0.25</v>
+      </c>
+      <c r="J23">
+        <v>94.841635199428893</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>43009</v>
       </c>
       <c r="B24" s="5">
         <v>162.4</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <v>18850.91</v>
+      </c>
+      <c r="G24">
+        <v>136392.89377273299</v>
+      </c>
+      <c r="H24">
+        <v>111.48159172576668</v>
+      </c>
+      <c r="I24">
+        <v>0.25</v>
+      </c>
+      <c r="J24">
+        <v>95.566017173232012</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>43040</v>
       </c>
       <c r="B25" s="5">
         <v>162.1</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <v>18279.150000000001</v>
+      </c>
+      <c r="G25">
+        <v>140657.11359792101</v>
+      </c>
+      <c r="H25">
+        <v>116.17593319616701</v>
+      </c>
+      <c r="I25">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J25">
+        <v>97.715751891433698</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>43070</v>
       </c>
       <c r="B26" s="5">
         <v>163.80000000000001</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <v>21082.9</v>
+      </c>
+      <c r="G26">
+        <v>146471.50810771901</v>
+      </c>
+      <c r="H26">
+        <v>114.37673558273501</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
+        <v>99.364119317832248</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>43101</v>
       </c>
       <c r="B27" s="5">
         <v>163.69999999999999</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <v>24915.5</v>
+      </c>
+      <c r="G27">
+        <v>133345.788783514</v>
+      </c>
+      <c r="H27">
+        <v>108.566788659387</v>
+      </c>
+      <c r="I27">
+        <v>3.5</v>
+      </c>
+      <c r="J27">
+        <v>100.74092666666665</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>43132</v>
       </c>
       <c r="B28" s="5">
         <v>163.9</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <v>18388.82</v>
+      </c>
+      <c r="G28">
+        <v>141036.723254107</v>
+      </c>
+      <c r="H28">
+        <v>103.09567917606533</v>
+      </c>
+      <c r="I28">
+        <v>5</v>
+      </c>
+      <c r="J28">
+        <v>103.48907833333334</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>43160</v>
       </c>
       <c r="B29" s="5">
         <v>164.8</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <v>19448.060000000001</v>
+      </c>
+      <c r="G29">
+        <v>143542.80216168999</v>
+      </c>
+      <c r="H29">
+        <v>101.84984973407366</v>
+      </c>
+      <c r="I29">
+        <v>6.416666666666667</v>
+      </c>
+      <c r="J29">
+        <v>106.07590966666667</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>43191</v>
       </c>
       <c r="B30" s="5">
         <v>170.6</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <v>21330.51</v>
+      </c>
+      <c r="G30">
+        <v>149462.87166954999</v>
+      </c>
+      <c r="H30">
+        <v>99.111692493173209</v>
+      </c>
+      <c r="I30">
+        <v>7.25</v>
+      </c>
+      <c r="J30">
+        <v>107.70491566666668</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>43221</v>
       </c>
       <c r="B31" s="5">
         <v>170.5</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <v>21898.03</v>
+      </c>
+      <c r="G31">
+        <v>133199.101081865</v>
+      </c>
+      <c r="H31">
+        <v>99.493675959023335</v>
+      </c>
+      <c r="I31">
+        <v>7.75</v>
+      </c>
+      <c r="J31">
+        <v>109.37374166666666</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>43252</v>
       </c>
       <c r="B32" s="5">
         <v>166.9</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <v>22329.75</v>
+      </c>
+      <c r="G32">
+        <v>140427.20612333901</v>
+      </c>
+      <c r="H32">
+        <v>95.050309070086385</v>
+      </c>
+      <c r="I32">
+        <v>7.75</v>
+      </c>
+      <c r="J32">
+        <v>111.18411400000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>43282</v>
       </c>
       <c r="B33" s="5">
         <v>166.1</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <v>22528.400000000001</v>
+      </c>
+      <c r="G33">
+        <v>142597.47099672799</v>
+      </c>
+      <c r="H33">
+        <v>93.315323369833138</v>
+      </c>
+      <c r="I33">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="J33">
+        <v>111.90916066666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>43313</v>
       </c>
       <c r="B34" s="5">
         <v>166.7</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <v>25960.01</v>
+      </c>
+      <c r="G34">
+        <v>148877.412001905</v>
+      </c>
+      <c r="H34">
+        <v>95.684950222222312</v>
+      </c>
+      <c r="I34">
+        <v>7</v>
+      </c>
+      <c r="J34">
+        <v>111.72943633333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>43344</v>
       </c>
       <c r="B35" s="5">
         <v>168.2</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <v>28366.99</v>
+      </c>
+      <c r="G35">
+        <v>135026.24537566199</v>
+      </c>
+      <c r="H35">
+        <v>95.308414261187238</v>
+      </c>
+      <c r="I35">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="J35">
+        <v>112.78706633333333</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>43374</v>
       </c>
       <c r="B36" s="5">
         <v>167.9</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <v>29895.87</v>
+      </c>
+      <c r="G36">
+        <v>145497.92528920801</v>
+      </c>
+      <c r="H36">
+        <v>93.662949021932434</v>
+      </c>
+      <c r="I36">
+        <v>5.833333333333333</v>
+      </c>
+      <c r="J36">
+        <v>113.671576</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>43405</v>
       </c>
       <c r="B37" s="5">
         <v>168.6</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <v>29942.23</v>
+      </c>
+      <c r="G37">
+        <v>148092.023399903</v>
+      </c>
+      <c r="H37">
+        <v>94.631791244387401</v>
+      </c>
+      <c r="I37">
+        <v>5.5</v>
+      </c>
+      <c r="J37">
+        <v>114.123537</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>43435</v>
       </c>
       <c r="B38" s="5">
         <v>168.7</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <v>28960.95</v>
+      </c>
+      <c r="G38">
+        <v>155150.116522667</v>
+      </c>
+      <c r="H38">
+        <v>93.427286849745371</v>
+      </c>
+      <c r="I38">
+        <v>5.083333333333333</v>
+      </c>
+      <c r="J38">
+        <v>114.05597233333333</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>43466</v>
       </c>
@@ -9514,7 +10094,7 @@
         <v>166.4</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>43497</v>
       </c>
@@ -9522,7 +10102,7 @@
         <v>167.4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>43525</v>
       </c>
@@ -9530,7 +10110,7 @@
         <v>170.6</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>43556</v>
       </c>
@@ -9538,7 +10118,7 @@
         <v>170.4</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>43586</v>
       </c>
@@ -9546,7 +10126,7 @@
         <v>171.8</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>43617</v>
       </c>
@@ -9554,7 +10134,7 @@
         <v>172.3</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>43647</v>
       </c>
@@ -9562,7 +10142,7 @@
         <v>172.4</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>43678</v>
       </c>
@@ -9570,7 +10150,7 @@
         <v>172.8</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>43709</v>
       </c>
@@ -9578,7 +10158,7 @@
         <v>171.7</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>43739</v>
       </c>
